--- a/stories/arbres/ATOM-EMO.LEX.007-03.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.007-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Lila attend avec papa. La chaise est dure. Ses jambes bougent. Ses mains froissent le manteau. Papa dit : tu es nerveuse. Le corps n'arrive pas à tenir. On peut demander une pause. Lila dit : je suis nerveuse. Je veux une pause. Papa l'écoute. Ils s'assoient près de la fenêtre. Lila souffle. Elle s'assoit. La pause aide. Papa dit : nerveux, ce n'est pas vilain. Une pause, c'est bien.</t>
+          <t>Lila attend avec papa. La chaise est dure. Ses jambes bougent. Ses mains froissent le manteau. Tu es nerveuse. Le corps n'arrive pas à tenir. On peut demander une pause. Je suis nerveuse. Je veux une pause. Papa l'écoute. Ils s'assoient près de la fenêtre. Lila souffle. Elle s'assoit. La pause aide. Nerveux, ce n'est pas vilain. Une pause, c'est bien.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Lila attend avec papa. La chaise est dure. Ses jambes bougent. Ses mains froissent le manteau.
+papa|Tu es nerveuse.
+narrateur|Le corps n'arrive pas à tenir. On peut demander une pause.
+enfant-f|Je suis nerveuse. Je veux une pause. Papa l'écoute.
+narrateur|Ils s'assoient près de la fenêtre. Lila souffle. Elle s'assoit. La pause aide.
+papa|Nerveux, ce n'est pas vilain.
+narrateur|Une pause, c'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1467,6 +1494,11 @@
           <t>question d'écoute, ne change pas le cours</t>
         </is>
       </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Lila n'arrive pas à tenir. Que fait-elle ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1491,7 +1523,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Lila a dit : je suis nerveuse. Elle a demandé une pause. Elle s'est assise.</t>
+          <t>Lila Je suis nerveuse. Elle a demandé une pause. Elle s'est assise.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1633,6 +1665,13 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Lila
+enfant-f|Je suis nerveuse. Elle a demandé une pause.
+narrateur|Elle s'est assise.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1834,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Papa donne la main. Ils rentrent.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +2001,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2041,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.007-03.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.007-03.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,7 @@
 narrateur|Une pause, c'est bien.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1505,7 @@
           <t>narrateur|Lila n'arrive pas à tenir. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1672,6 +1679,7 @@
 narrateur|Elle s'est assise.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1839,6 +1847,7 @@
           <t>narrateur|Papa donne la main. Ils rentrent.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2006,6 +2015,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2024,7 +2034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2048,6 +2058,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2249,6 +2273,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-EMO.LEX.007-03.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.007-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lila est nerveuse et demande une pause</t>
+          <t>Nina demande une pause</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>L'horloge tique. Nina froisse le manteau. Elle nomme nerveuse, demande une pause, s'assoit près de la fenêtre.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Lila attend avec papa. La chaise est dure. Ses jambes bougent. Ses mains froissent le manteau. Tu es nerveuse. Le corps n'arrive pas à tenir. On peut demander une pause. Je suis nerveuse. Je veux une pause. Papa l'écoute. Ils s'assoient près de la fenêtre. Lila souffle. Elle s'assoit. La pause aide. Nerveux, ce n'est pas vilain. Une pause, c'est bien.</t>
+          <t>L'horloge fait tic, tic, tic. Chaque tic est tout petit, tout régulier. Les magazines sont froids sous les doigts. Leurs pages sont lisses, un peu brillantes. La chaise est dure. Le bois appuie dans le dos. Une plante verte attend près de la fenêtre. Ses feuilles sont larges et brillantes. On attend un peu, Nina. L'horloge parle. Oui. Elle compte le temps. Tu as vu la plante ? Ses feuilles brillent. La fenêtre lui donne de la lumière. En ce moment, Nina attend avec papa. Ils sont dans la salle d'attente. Nina froisse le manteau sur ses genoux. Le tissu fait un bruit de papier. Ses jambes bougent. Ses talons tapent le sol, tout bas. Le corps n'arrive pas à tenir. Tu es nerveuse, Nina. Nerveux, on peut le dire. On peut demander une pause. Je suis nerveuse. Je veux une pause. Je t'écoute. On s'assoit près de la fenêtre. Ils s'assoient près de la fenêtre. Nina s'assoit. Elle pose les pieds au sol. Les pieds sont posés. Tu souffles avec moi ? Oui, papa. Nina souffle. Le manteau s'arrête de froisser. La pause aide. Nerveux, ce n'est pas vilain. Une pause, c'est bien. Bravo, Nina. C'est du bon travail. Tu as demandé la pause ? Oui. Je suis nerveuse. Tu as nommé. Tu t'es assise. L'horloge fait encore tic, tic. Mais le tic est plus loin, maintenant. Tu regardes la plante ? Une feuille touche la vitre. Oui. Elle aime la lumière. Mes jambes bougent moins. La pause a aidé. Un rayon pâle traverse la vitre. Il réchauffe le bois de la chaise. On reste près de la fenêtre ? Oui, papa. On reste. Les magazines restent empilés, froids. Nina laisse le manteau sur ses genoux, sans le froisser.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,16 +1324,75 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Lila attend avec papa. La chaise est dure. Ses jambes bougent. Ses mains froissent le manteau.
-papa|Tu es nerveuse.
-narrateur|Le corps n'arrive pas à tenir. On peut demander une pause.
-enfant-f|Je suis nerveuse. Je veux une pause. Papa l'écoute.
-narrateur|Ils s'assoient près de la fenêtre. Lila souffle. Elle s'assoit. La pause aide.
+          <t>narrateur|L'horloge fait tic, tic, tic.
+narrateur|Chaque tic est tout petit, tout régulier.
+narrateur|Les magazines sont froids sous les doigts.
+narrateur|Leurs pages sont lisses, un peu brillantes.
+narrateur|La chaise est dure.
+narrateur|Le bois appuie dans le dos.
+narrateur|Une plante verte attend près de la fenêtre.
+narrateur|Ses feuilles sont larges et brillantes.
+papa|On attend un peu, Nina.
+enfant-f|L'horloge parle.
+papa|Oui.
+papa|Elle compte le temps.
+papa|Tu as vu la plante ?
+enfant-f|Ses feuilles brillent.
+papa|La fenêtre lui donne de la lumière.
+narrateur|En ce moment, Nina attend avec papa.
+narrateur|Ils sont dans la salle d'attente.
+narrateur|Nina froisse le manteau sur ses genoux.
+narrateur|Le tissu fait un bruit de papier.
+narrateur|Ses jambes bougent.
+narrateur|Ses talons tapent le sol, tout bas.
+narrateur|Le corps n'arrive pas à tenir.
+papa|Tu es nerveuse, Nina.
+papa|Nerveux, on peut le dire.
+papa|On peut demander une pause.
+enfant-f|Je suis nerveuse.
+enfant-f|Je veux une pause.
+papa|Je t'écoute.
+papa|On s'assoit près de la fenêtre.
+narrateur|Ils s'assoient près de la fenêtre.
+narrateur|Nina s'assoit.
+narrateur|Elle pose les pieds au sol.
+papa|Les pieds sont posés.
+papa|Tu souffles avec moi ?
+enfant-f|Oui, papa.
+narrateur|Nina souffle.
+narrateur|Le manteau s'arrête de froisser.
+narrateur|La pause aide.
 papa|Nerveux, ce n'est pas vilain.
-narrateur|Une pause, c'est bien.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+papa|Une pause, c'est bien.
+papa|Bravo, Nina.
+papa|C'est du bon travail.
+papa|Tu as demandé la pause ?
+enfant-f|Oui.
+enfant-f|Je suis nerveuse.
+papa|Tu as nommé.
+papa|Tu t'es assise.
+narrateur|L'horloge fait encore tic, tic.
+narrateur|Mais le tic est plus loin, maintenant.
+papa|Tu regardes la plante ?
+enfant-f|Une feuille touche la vitre.
+papa|Oui.
+papa|Elle aime la lumière.
+enfant-f|Mes jambes bougent moins.
+papa|La pause a aidé.
+narrateur|Un rayon pâle traverse la vitre.
+narrateur|Il réchauffe le bois de la chaise.
+papa|On reste près de la fenêtre ?
+enfant-f|Oui, papa.
+papa|On reste.
+narrateur|Les magazines restent empilés, froids.
+narrateur|Nina laisse le manteau sur ses genoux, sans le froisser.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>horloge_salle</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1346,7 +1417,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Lila n'arrive pas à tenir. Que fait-elle ?</t>
+          <t>Nina n'arrive pas à tenir. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1502,7 +1573,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Lila n'arrive pas à tenir. Que fait-elle ?</t>
+          <t>narrateur|Nina n'arrive pas à tenir.
+narrateur|Que fait-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1530,7 +1602,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Lila Je suis nerveuse. Elle a demandé une pause. Elle s'est assise.</t>
+          <t>Nina a nommé : nerveuse. Nerveux, on peut le dire. Elle a demandé une pause. Elle s'est assise. Je suis nerveuse. J'ai demandé une pause. Bravo, Nina. Tu as demandé une pause. C'est du bon travail. Tu t'es assise. Les pieds sont au sol ? Oui, papa.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1674,9 +1746,18 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Lila
-enfant-f|Je suis nerveuse. Elle a demandé une pause.
-narrateur|Elle s'est assise.</t>
+          <t>narrateur|Nina a nommé : nerveuse.
+narrateur|Nerveux, on peut le dire.
+narrateur|Elle a demandé une pause.
+narrateur|Elle s'est assise.
+enfant-f|Je suis nerveuse.
+enfant-f|J'ai demandé une pause.
+papa|Bravo, Nina.
+papa|Tu as demandé une pause.
+papa|C'est du bon travail.
+papa|Tu t'es assise.
+papa|Les pieds sont au sol ?
+enfant-f|Oui, papa.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1704,7 +1785,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Papa donne la main. Ils rentrent.</t>
+          <t>Papa donne la main. Ils rentrent. On marche tout doux ? Oui. Mes jambes sont calmes. La pause a aidé. L'horloge reste derrière eux. La plante garde sa feuille contre la vitre. Tu restes près de moi ? Oui, papa. Le manteau ne froisse plus. Il sent encore un peu le savon.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1844,7 +1925,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Papa donne la main. Ils rentrent.</t>
+          <t>narrateur|Papa donne la main.
+narrateur|Ils rentrent.
+papa|On marche tout doux ?
+enfant-f|Oui.
+enfant-f|Mes jambes sont calmes.
+papa|La pause a aidé.
+narrateur|L'horloge reste derrière eux.
+narrateur|La plante garde sa feuille contre la vitre.
+papa|Tu restes près de moi ?
+enfant-f|Oui, papa.
+narrateur|Le manteau ne froisse plus.
+narrateur|Il sent encore un peu le savon.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1872,7 +1964,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai demandé une pause. J'étais nerveuse. Nerveux, ce n'est pas vilain. Bravo. Tu as fait du bon travail. Le tic de l'horloge est loin, maintenant. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2012,7 +2104,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai demandé une pause.
+enfant-f|J'étais nerveuse.
+papa|Nerveux, ce n'est pas vilain.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Le tic de l'horloge est loin, maintenant.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2034,7 +2132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2072,6 +2170,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.007-03.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.007-03.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>L'horloge fait tic, tic, tic. Chaque tic est tout petit, tout régulier. Les magazines sont froids sous les doigts. Leurs pages sont lisses, un peu brillantes. La chaise est dure. Le bois appuie dans le dos. Une plante verte attend près de la fenêtre. Ses feuilles sont larges et brillantes. On attend un peu, Nina. L'horloge parle. Oui. Elle compte le temps. Tu as vu la plante ? Ses feuilles brillent. La fenêtre lui donne de la lumière. En ce moment, Nina attend avec papa. Ils sont dans la salle d'attente. Nina froisse le manteau sur ses genoux. Le tissu fait un bruit de papier. Ses jambes bougent. Ses talons tapent le sol, tout bas. Le corps n'arrive pas à tenir. Tu es nerveuse, Nina. Nerveux, on peut le dire. On peut demander une pause. Je suis nerveuse. Je veux une pause. Je t'écoute. On s'assoit près de la fenêtre. Ils s'assoient près de la fenêtre. Nina s'assoit. Elle pose les pieds au sol. Les pieds sont posés. Tu souffles avec moi ? Oui, papa. Nina souffle. Le manteau s'arrête de froisser. La pause aide. Nerveux, ce n'est pas vilain. Une pause, c'est bien. Bravo, Nina. C'est du bon travail. Tu as demandé la pause ? Oui. Je suis nerveuse. Tu as nommé. Tu t'es assise. L'horloge fait encore tic, tic. Mais le tic est plus loin, maintenant. Tu regardes la plante ? Une feuille touche la vitre. Oui. Elle aime la lumière. Mes jambes bougent moins. La pause a aidé. Un rayon pâle traverse la vitre. Il réchauffe le bois de la chaise. On reste près de la fenêtre ? Oui, papa. On reste. Les magazines restent empilés, froids. Nina laisse le manteau sur ses genoux, sans le froisser.</t>
+          <t>L'horloge fait tic, tic, tic. Chaque tic est tout petit, tout régulier. Les magazines sont froids sous les doigts. Leurs pages sont lisses, un peu brillantes. La chaise est dure. Le bois appuie dans le dos. Une plante verte attend près de la fenêtre. Ses feuilles sont larges et brillantes. On attend un peu, Nina. L'horloge parle. Oui. Elle compte le temps. Tu as vu la plante ? Ses feuilles brillent. La fenêtre lui donne de la lumière. En ce moment, Nina attend avec papa. Ils sont dans la salle d'attente. Nina froisse le manteau sur ses genoux. Le tissu fait un bruit de papier. Ses jambes bougent. Ses talons tapent le sol, tout bas. Le corps n'arrive pas à tenir. Tu es nerveuse, Nina. Nerveux, on peut le dire. On peut demander une pause. Je suis nerveuse. Je veux une pause. Je t'écoute. On s'assoit près de la fenêtre. Ils s'assoient près de la fenêtre. Nina s'assoit. Elle pose les pieds au sol. Les pieds sont posés. Tu souffles avec moi ? Oui, papa. Nina souffle. Le manteau s'arrête de froisser. La pause aide. Nerveux, ce n'est pas vilain. Une pause, c'est bien. Bravo, Nina. Tu as demandé la pause ? Oui. Je suis nerveuse. Tu as nommé. Tu t'es assise. L'horloge fait encore tic, tic. Mais le tic est plus loin, maintenant. Tu regardes la plante ? Une feuille touche la vitre. Oui. Elle aime la lumière. Mes jambes bougent moins. La pause a aidé. Un rayon pâle traverse la vitre. Il réchauffe le bois de la chaise. On reste près de la fenêtre ? Oui, papa. On reste. Les magazines restent empilés, froids. Nina laisse le manteau sur ses genoux, sans le froisser.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Lila attend avec papa. La chaise est dure. Ses jambes bougent. Ses mains froissent le manteau. Papa dit : tu es nerveuse. Le corps n'arrive pas à tenir. On peut demander une pause. Lila dit : je suis nerveuse. Je veux une pause. Papa l'écoute. Ils s'assoient près de la fenêtre. Lila souffle. Elle s'assoit. La pause aide. Papa dit : &lt;emphasis level="moderate"&gt;nerveux&lt;/emphasis&gt;, ce n'est pas vilain. Une pause, c'est bien.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>L'horloge fait tic, tic, tic. Chaque tic est tout petit, tout régulier. Les magazines sont froids sous les doigts. Leurs pages sont lisses, un peu brillantes. La chaise est dure. Le bois appuie dans le dos. Une plante verte attend près de la fenêtre. Ses feuilles sont larges et brillantes. On attend un peu, Nina. L'horloge parle. Oui. Elle compte le temps. Tu as vu la plante ? Ses feuilles brillent. La fenêtre lui donne de la lumière. En ce moment, Nina attend avec papa. Ils sont dans la salle d'attente. Nina froisse le manteau sur ses genoux. Le tissu fait un bruit de papier. Ses jambes bougent. Ses talons tapent le sol, tout bas. Le corps n'arrive pas à tenir. Tu es nerveuse, Nina. Nerveux, on peut le dire. On peut demander une pause. Je suis nerveuse. Je veux une pause. Je t'écoute. On s'assoit près de la fenêtre. Ils s'assoient près de la fenêtre. Nina s'assoit. Elle pose les pieds au sol. Les pieds sont posés. Tu souffles avec moi ? Oui, papa. Nina souffle. Le manteau s'arrête de froisser. La pause aide. Nerveux, ce n'est pas vilain. Une pause, c'est bien. Bravo, Nina. Tu as demandé la pause ? Oui. Je suis nerveuse. Tu as nommé. Tu t'es assise. L'horloge fait encore tic, tic. Mais le tic est plus loin, maintenant. Tu regardes la plante ? Une feuille touche la vitre. Oui. Elle aime la lumière. Mes jambes bougent moins. La pause a aidé. Un rayon pâle traverse la vitre. Il réchauffe le bois de la chaise. On reste près de la fenêtre ? Oui, papa. On reste. Les magazines restent empilés, froids. Nina laisse le manteau sur ses genoux, sans le froisser.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1365,7 +1365,6 @@
 papa|Nerveux, ce n'est pas vilain.
 papa|Une pause, c'est bien.
 papa|Bravo, Nina.
-papa|C'est du bon travail.
 papa|Tu as demandé la pause ?
 enfant-f|Oui.
 enfant-f|Je suis nerveuse.
@@ -1422,7 +1421,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Lila n'arrive pas à tenir. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina n'arrive pas à tenir. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1577,7 +1576,6 @@
 narrateur|Que fait-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1602,12 +1600,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nina a nommé : nerveuse. Nerveux, on peut le dire. Elle a demandé une pause. Elle s'est assise. Je suis nerveuse. J'ai demandé une pause. Bravo, Nina. Tu as demandé une pause. C'est du bon travail. Tu t'es assise. Les pieds sont au sol ? Oui, papa.</t>
+          <t>Nina a nommé : nerveuse. Nerveux, on peut le dire. Elle a demandé une pause. Elle s'est assise. Je suis nerveuse. J'ai demandé une pause. Bravo, Nina. Tu as demandé une pause. Tu t'es assise. Les pieds sont au sol ? Oui, papa.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Lila a dit : je suis nerveuse. Elle a demandé une &lt;emphasis level="moderate"&gt;pause&lt;/emphasis&gt;. Elle s'est assise.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina a nommé : nerveuse. Nerveux, on peut le dire. Elle a demandé une pause. Elle s'est assise. Je suis nerveuse. J'ai demandé une pause. Bravo, Nina. Tu as demandé une pause. Tu t'es assise. Les pieds sont au sol ? Oui, papa.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1754,13 +1752,11 @@
 enfant-f|J'ai demandé une pause.
 papa|Bravo, Nina.
 papa|Tu as demandé une pause.
-papa|C'est du bon travail.
 papa|Tu t'es assise.
 papa|Les pieds sont au sol ?
 enfant-f|Oui, papa.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1790,7 +1786,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Papa donne la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;. Ils rentrent.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa donne la main. Ils rentrent. On marche tout doux ? Oui. Mes jambes sont calmes. La pause a aidé. L'horloge reste derrière eux. La plante garde sa feuille contre la vitre. Tu restes près de moi ? Oui, papa. Le manteau ne froisse plus. Il sent encore un peu le savon.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1939,7 +1935,6 @@
 narrateur|Il sent encore un peu le savon.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1964,12 +1959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai demandé une pause. J'étais nerveuse. Nerveux, ce n'est pas vilain. Bravo. Tu as fait du bon travail. Le tic de l'horloge est loin, maintenant. L'histoire est finie.</t>
+          <t>J'ai demandé une pause. J'étais nerveuse. Nerveux, ce n'est pas vilain. Bravo. Le tic de l'horloge est loin, maintenant.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai demandé une pause. J'étais nerveuse. Nerveux, ce n'est pas vilain. Bravo. Le tic de l'horloge est loin, maintenant.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2108,12 +2103,9 @@
 enfant-f|J'étais nerveuse.
 papa|Nerveux, ce n'est pas vilain.
 papa|Bravo.
-papa|Tu as fait du bon travail.
-narrateur|Le tic de l'horloge est loin, maintenant.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le tic de l'horloge est loin, maintenant.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2132,7 +2124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2177,6 +2169,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.007-03.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.007-03.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Lila, papa</t>
+          <t>Nina, papa</t>
         </is>
       </c>
     </row>
